--- a/artfynd/A 5642-2024 artfynd.xlsx
+++ b/artfynd/A 5642-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,10 +2437,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>70094631</v>
+        <v>55047291</v>
       </c>
       <c r="B17" t="n">
-        <v>57903</v>
+        <v>57323</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2448,26 +2448,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102110</v>
+        <v>100112</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Ljungpipare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Pluvialis apricaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2513,22 +2513,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2018-03-23</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2018-03-23</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2548,39 +2548,39 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Roger Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103604349</v>
+        <v>70094631</v>
       </c>
       <c r="B18" t="n">
-        <v>58559</v>
+        <v>57903</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102120</v>
+        <v>102110</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rödstrupig piplärka</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthus cervinus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pallas, 1811)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2592,10 +2592,9 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sommarsäte vid bron, Södra Ljunga, Sm</t>
@@ -2632,22 +2631,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2018-03-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>2018-03-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2667,51 +2666,51 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson, Anders Carlsson, Jonas Strandberg</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112079151</v>
+        <v>103604349</v>
       </c>
       <c r="B19" t="n">
-        <v>58607</v>
+        <v>58559</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102124</v>
+        <v>102120</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vinterhämpling</t>
+          <t>Rödstrupig piplärka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Linaria flavirostris</t>
+          <t>Anthus cervinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1811)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2751,12 +2750,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-10-19</t>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2022-09-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2771,56 +2780,56 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Johan Sandström</t>
+          <t>Roger Karlsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson, Conny Christensen</t>
+          <t>Roger Karlsson, Kerstin Karlsson, Anders Carlsson, Jonas Strandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>79976168</v>
+        <v>112079151</v>
       </c>
       <c r="B20" t="n">
-        <v>58671</v>
+        <v>58607</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102126</v>
+        <v>102124</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ortolansparv</t>
+          <t>Vinterhämpling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Emberiza hortulana</t>
+          <t>Linaria flavirostris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2860,27 +2869,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2022-10-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2019-09-18</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Hördes vid ett tiotal tillfällen.</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2895,39 +2889,39 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Roger Karlsson</t>
+          <t>Johan Sandström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson, Conny Christensen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96417817</v>
+        <v>79976168</v>
       </c>
       <c r="B21" t="n">
-        <v>57981</v>
+        <v>58671</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102611</v>
+        <v>102126</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stenfalk</t>
+          <t>Ortolansparv</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Falco columbarius</t>
+          <t>Emberiza hortulana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2944,7 +2938,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2984,22 +2978,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2021-10-02</t>
+          <t>2019-09-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2021-10-02</t>
+          <t>2019-09-18</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hördes vid ett tiotal tillfällen.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3026,10 +3025,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>70047880</v>
+        <v>96417817</v>
       </c>
       <c r="B22" t="n">
-        <v>58129</v>
+        <v>57981</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,21 +3036,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102623</v>
+        <v>102611</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Stenfalk</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Falco columbarius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3063,9 +3062,10 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>sträckande N</t>
-        </is>
-      </c>
+          <t>sträckande S</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sommarsäte vid bron, Södra Ljunga, Sm</t>
@@ -3102,22 +3102,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2018-03-19</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2018-03-19</t>
+          <t>2021-10-02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3144,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128082771</v>
+        <v>70047880</v>
       </c>
       <c r="B23" t="n">
-        <v>58039</v>
+        <v>58129</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102626</v>
+        <v>102623</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3181,10 +3181,9 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>sträckande N</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Sommarsäte vid bron, Södra Ljunga, Sm</t>
@@ -3221,17 +3220,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2018-03-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2018-03-19</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3256,34 +3255,34 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson, Anders Carlsson, Jonas Strandberg</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112112342</v>
+        <v>128082771</v>
       </c>
       <c r="B24" t="n">
-        <v>57105</v>
+        <v>58039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102932</v>
+        <v>102626</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3293,14 +3292,14 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3340,22 +3339,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-15</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3375,44 +3374,44 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson, Anders Carlsson, Conny Christensen</t>
+          <t>Roger Karlsson, Kerstin Karlsson, Anders Carlsson, Jonas Strandberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>55047297</v>
+        <v>112112342</v>
       </c>
       <c r="B25" t="n">
-        <v>57317</v>
+        <v>57105</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102952</v>
+        <v>102932</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -3422,6 +3421,7 @@
           <t>förbiflygande</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sommarsäte vid bron, Södra Ljunga, Sm</t>
@@ -3458,22 +3458,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2015-09-04</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2015-09-04</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3493,54 +3493,53 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson, Anders Carlsson, Conny Christensen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112132253</v>
+        <v>55047297</v>
       </c>
       <c r="B26" t="n">
-        <v>57238</v>
+        <v>57317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102972</v>
+        <v>102952</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Turkduva</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Streptopelia decaocto</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Frivaldszky, 1838)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sommarsäte vid bron, Södra Ljunga, Sm</t>
@@ -3577,22 +3576,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-16</t>
+          <t>2015-09-04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3612,39 +3611,39 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Carlsson</t>
+          <t>Roger Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112132235</v>
+        <v>112132253</v>
       </c>
       <c r="B27" t="n">
-        <v>57947</v>
+        <v>57238</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102977</v>
+        <v>102972</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Turkduva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Streptopelia decaocto</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Frivaldszky, 1838)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3656,7 +3655,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3738,27 +3737,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>79912249</v>
+        <v>112132235</v>
       </c>
       <c r="B28" t="n">
-        <v>58209</v>
+        <v>57947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102980</v>
+        <v>102977</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3768,7 +3767,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3815,22 +3814,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2023-09-16</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3850,17 +3849,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Anders Carlsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>96281643</v>
+        <v>79912249</v>
       </c>
       <c r="B29" t="n">
-        <v>58541</v>
+        <v>58209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3868,16 +3867,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102987</v>
+        <v>102980</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3887,14 +3886,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3934,22 +3933,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3976,10 +3975,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>96327392</v>
+        <v>96281643</v>
       </c>
       <c r="B30" t="n">
-        <v>58497</v>
+        <v>58541</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3987,33 +3986,33 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102990</v>
+        <v>102987</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4053,17 +4052,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2021-09-26</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4088,34 +4087,34 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson, Anders Carlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119243154</v>
+        <v>96327392</v>
       </c>
       <c r="B31" t="n">
-        <v>58463</v>
+        <v>58497</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102995</v>
+        <v>102990</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4125,14 +4124,14 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4172,22 +4171,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2021-09-26</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4207,51 +4206,51 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson, Anders Carlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112768518</v>
+        <v>119243154</v>
       </c>
       <c r="B32" t="n">
-        <v>58393</v>
+        <v>58463</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102999</v>
+        <v>102995</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4291,22 +4290,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2024-08-20</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4333,44 +4332,44 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>106629108</v>
+        <v>112768518</v>
       </c>
       <c r="B33" t="n">
-        <v>58327</v>
+        <v>58393</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4410,22 +4409,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-02-11</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-02-11</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4452,27 +4451,27 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96281205</v>
+        <v>106629108</v>
       </c>
       <c r="B34" t="n">
-        <v>58112</v>
+        <v>58327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4482,14 +4481,14 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4529,22 +4528,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2023-02-11</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
+          <t>2023-02-11</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4571,10 +4570,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112292061</v>
+        <v>96281205</v>
       </c>
       <c r="B35" t="n">
-        <v>58114</v>
+        <v>58112</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4582,21 +4581,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4648,12 +4647,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2021-09-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4680,37 +4689,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128721178</v>
+        <v>112292061</v>
       </c>
       <c r="B36" t="n">
-        <v>58082</v>
+        <v>58114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103035</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4757,22 +4766,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4792,34 +4791,34 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson, Anders Carlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119688146</v>
+        <v>128721178</v>
       </c>
       <c r="B37" t="n">
-        <v>58353</v>
+        <v>58082</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103037</v>
+        <v>103035</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Kråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Corvus corone</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4829,14 +4828,14 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4876,22 +4875,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4911,51 +4910,51 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson, Anders Carlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>96298521</v>
+        <v>119688146</v>
       </c>
       <c r="B38" t="n">
-        <v>58636</v>
+        <v>58353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103044</v>
+        <v>103037</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -4995,17 +4994,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-09-25</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-09-25</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
@@ -5030,53 +5029,54 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Roger Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>68395644</v>
+        <v>96298521</v>
       </c>
       <c r="B39" t="n">
-        <v>58676</v>
+        <v>58636</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>sträckande S</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sommarsäte vid bron, Södra Ljunga, Sm</t>
@@ -5113,12 +5113,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2017-11-04</t>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2017-11-04</t>
+          <t>2021-09-25</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5145,37 +5155,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96281237</v>
+        <v>68395644</v>
       </c>
       <c r="B40" t="n">
-        <v>58649</v>
+        <v>58676</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103057</v>
+        <v>103055</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -5185,7 +5195,6 @@
           <t>stationär</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sommarsäte vid bron, Södra Ljunga, Sm</t>
@@ -5222,22 +5231,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2017-11-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2017-11-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5264,32 +5263,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>79912213</v>
+        <v>96281237</v>
       </c>
       <c r="B41" t="n">
-        <v>57892</v>
+        <v>58649</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103060</v>
+        <v>103057</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brun glada</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Milvus migrans</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5297,15 +5296,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>sträckande S</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5345,22 +5340,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5387,49 +5382,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>60676242</v>
+        <v>79912213</v>
       </c>
       <c r="B42" t="n">
-        <v>43219</v>
+        <v>57892</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>201028</v>
+        <v>103060</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre tåtelsmygare</t>
+          <t>Brun glada</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thymelicus lineola</t>
+          <t>Milvus migrans</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ochsenheimer, 1808)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>imago/adult</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5469,12 +5463,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2016-07-23</t>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2016-07-23</t>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5494,39 +5498,39 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>59987916</v>
+        <v>60676242</v>
       </c>
       <c r="B43" t="n">
-        <v>43378</v>
+        <v>43219</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>201075</v>
+        <v>201028</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5535,7 +5539,11 @@
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
@@ -5579,12 +5587,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
+          <t>2016-07-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
+          <t>2016-07-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5604,52 +5612,48 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>60676234</v>
+        <v>59987916</v>
       </c>
       <c r="B44" t="n">
-        <v>43258</v>
+        <v>43378</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>201129</v>
+        <v>201075</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitfläckig guldvinge</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycaena virgaureae</t>
+          <t>Boloria selene</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
@@ -5693,12 +5697,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2016-07-23</t>
+          <t>2016-06-05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2016-07-23</t>
+          <t>2016-06-05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5718,17 +5722,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kerstin Karlsson, Roger Karlsson</t>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>103632740</v>
+        <v>60676234</v>
       </c>
       <c r="B45" t="n">
-        <v>57738</v>
+        <v>43258</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5736,33 +5740,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>205497</v>
+        <v>201129</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ägretthäger</t>
+          <t>Vitfläckig guldvinge</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ardea alba</t>
+          <t>Lycaena virgaureae</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5802,22 +5811,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2016-07-23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-09-18</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2016-07-23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5837,17 +5836,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Roger Karlsson, Kerstin Karlsson</t>
+          <t>Kerstin Karlsson, Roger Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>87930189</v>
+        <v>103632740</v>
       </c>
       <c r="B46" t="n">
-        <v>56689</v>
+        <v>57738</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5855,33 +5854,36 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>206046</v>
+        <v>205497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Ägretthäger</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alces alces</t>
+          <t>Ardea alba</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sommarsäte vid bron, Södra Ljunga, Sm</t>
@@ -5918,12 +5920,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2020-09-10</t>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5947,6 +5959,112 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>87930189</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sommarsäte vid bron, Södra Ljunga, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>438872</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6291052</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ljungby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Södra Ljunga</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2020-09-10</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2020-09-10</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Roger Karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Roger Karlsson, Kerstin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
